--- a/AAAGameData/Languages/Indonesian.xlsx
+++ b/AAAGameData/Languages/Indonesian.xlsx
@@ -11,257 +11,400 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Anonymous</d:author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">勾选锁定此行,锁定后将强制保留</t>
-        </d:r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Key</t>
-        </d:r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Value, 当值为空时, [一键翻译]会自动填充Value值</t>
-        </d:r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
-  <si>
-    <t>ArrowMakeupGuideUIForm.go</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip1</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip2</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.Title</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.account</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.continue</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.payment</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.rebind</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.tips</t>
-  </si>
-  <si>
-    <t>ArrowMakeupOrdemUIForm.record</t>
-  </si>
-  <si>
-    <t>ArrowMakeupTipsUIForm.Text_Title</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.makeup</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.play</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.title</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.curBankInfo</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.ratio</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.tile</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.title_text</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.GameOver</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.restart</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.Revive</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.elimanateHit</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.ItemAutoRemoveFail</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.LevelTxt</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.makeuptxt</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+  <si>
+    <t>AddBallsUIForm.ballTxt</t>
+  </si>
+  <si>
+    <t>+5 Bola</t>
+  </si>
+  <si>
+    <t>AddBallsUIForm.continueTxt</t>
+  </si>
+  <si>
+    <t>Lanjutkan?</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
+    <t>Kebijakan Privasi</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.claim</t>
   </si>
   <si>
-    <t>ArrowRewardDialogUIForm.Continue</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.NextLevel</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.claim</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.Notchanks</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardUIForm.check</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.Confirm</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title_1</t>
+    <t>Klaim</t>
+  </si>
+  <si>
+    <t>ArrowRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Selamat</t>
   </si>
   <si>
     <t>ArrowSettingController.OFF</t>
   </si>
   <si>
+    <t>nonaktif</t>
+  </si>
+  <si>
     <t>ArrowSettingController.ON</t>
   </si>
   <si>
-    <t>ArrowSettingDialog.Home</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Music</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Privacy</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Resume</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Sound</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Text_Title</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Vibrate</t>
+    <t>aktif</t>
   </si>
   <si>
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
+    <t>Tarik Dana</t>
+  </si>
+  <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
+    <t>Selamat kepada pemain {0} karena telah menyelesaikan ({1}) dan mengklaim {2}.</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
     <t>Enteraccountnumber</t>
   </si>
   <si>
+    <t>Masukkan akun Anda</t>
+  </si>
+  <si>
     <t>EnterCPF</t>
   </si>
   <si>
+    <t>Masukkan CPF</t>
+  </si>
+  <si>
     <t>Enteremail</t>
   </si>
   <si>
+    <t>Konfirmasi email</t>
+  </si>
+  <si>
     <t>EnterFullName</t>
   </si>
   <si>
+    <t>Masukkan Nama Lengkap</t>
+  </si>
+  <si>
     <t>EnterPayPalaccount</t>
   </si>
   <si>
+    <t>Masukkan akun PayPal</t>
+  </si>
+  <si>
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
+    <t>Ketuk benda itu dan tembakkan meriam!</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>Beranda</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>Pengaturan</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>Misi</t>
   </si>
   <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
+    <t>Masukkan alamat email yang valid</t>
+  </si>
+  <si>
     <t>InfoErrTips2</t>
   </si>
   <si>
+    <t>Masukkan CPF yang valid</t>
+  </si>
+  <si>
     <t>InfoErrTips3</t>
   </si>
   <si>
+    <t>Akun PayPal harus berupa alamat email yang valid</t>
+  </si>
+  <si>
     <t>InfoErrTips4</t>
   </si>
   <si>
+    <t>Masukkan nama lengkap Anda</t>
+  </si>
+  <si>
     <t>InfoErrTips5</t>
   </si>
   <si>
+    <t>Masukkan nomor rekening Anda</t>
+  </si>
+  <si>
     <t>InfoErrTips6</t>
   </si>
   <si>
+    <t>Pilih metode pembayaran</t>
+  </si>
+  <si>
     <t>InfoErrTips7</t>
   </si>
   <si>
+    <t>Informasi pembayaran berhasil disimpan</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>Level {0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>Selesai</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.next</t>
+  </si>
+  <si>
+    <t>Berikutnya</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
+    <t>Maaf, penukaran gagal.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t>Pastikan akun PayPal yang dimasukkan di kedua kolom sama.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
+    <t>Masukkan email dengan format yang benar.</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>Penarikan sedang diproses</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Metode Pembayaran</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
+    <t>Selesaikan level {0} untuk menarik dana</t>
+  </si>
+  <si>
     <t>MakeUpStep2</t>
+  </si>
+  <si>
+    <t>Kumpulkan {0} lagi untuk menarik dana</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>Masukkan</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
+    <t>Riwayat</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
+    <t>Saldo {0}=$1</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
+    <t>Tonton iklan untuk mendapatkan item game dari peti.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>Keluar sekarang akan membuat Anda kehilangan satu nyawa.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>Keluar?</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
+  </si>
+  <si>
+    <t>Lanjutkan</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.privacy</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.quit</t>
+  </si>
+  <si>
+    <t>Keluar</t>
+  </si>
+  <si>
+    <t>TaskItem.infoTxt</t>
+  </si>
+  <si>
+    <t>Selesaikan {0} level!</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm.title</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>Nyawa Tambahan</t>
+  </si>
+  <si>
+    <t>AddPropUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>Roket</t>
+  </si>
+  <si>
+    <t>PlayLoadingUIForm.loading</t>
+  </si>
+  <si>
+    <t>Memuat...</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quit</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.avatarTxt</t>
+  </si>
+  <si>
+    <t>Pilih avatar:</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterDesc</t>
+  </si>
+  <si>
+    <t>Masukkan akun PayPal Anda</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterAgainDesc</t>
+  </si>
+  <si>
+    <t>Masukkan kembali akun PayPal</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.confirm</t>
+  </si>
+  <si>
+    <t>Konfirmasi</t>
+  </si>
+  <si>
+    <t>TaskItem.adTxt</t>
+  </si>
+  <si>
+    <t>Tonton iklan!</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>Gratis</t>
+  </si>
+  <si>
+    <t>TaskItem.go</t>
+  </si>
+  <si>
+    <t>Mulai</t>
+  </si>
+  <si>
+    <t>cashoutHint</t>
+  </si>
+  <si>
+    <t>Anda harus menyelesaikan {0} level dan mengumpulkan saldo sebesar {1} sebelum dapat mengklaimnya.</t>
+  </si>
+  <si>
+    <t>MakeupItem.cashout</t>
+  </si>
+  <si>
+    <t>GuidTxt2</t>
+  </si>
+  <si>
+    <t>Hancurkan semua benda sebelum tembakan habis!</t>
+  </si>
+  <si>
+    <t>MakeupRecordItem.bouns</t>
+  </si>
+  <si>
+    <t>Total Hadiah Hari Ini</t>
+  </si>
+  <si>
+    <t>PlayUIForm.txtHint</t>
+  </si>
+  <si>
+    <t>Ketuk benda-benda di atas meja</t>
+  </si>
+  <si>
+    <t>MakeupItem.reach</t>
+  </si>
+  <si>
+    <t>Saldo yang Diperlukan</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.desc</t>
+  </si>
+  <si>
+    <t>Pilih Booster:</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm.desc</t>
+  </si>
+  <si>
+    <t>Terima kasih atas donasi Anda yang murah hati!</t>
+  </si>
+  <si>
+    <t>giftHint</t>
+  </si>
+  <si>
+    <t>Kumpulkan peti harta karun</t>
   </si>
 </sst>
 </file>
@@ -297,9 +440,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -321,27 +462,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -361,35 +502,35 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,15 +546,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,11 +566,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,23 +646,23 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,7 +678,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
@@ -545,7 +686,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,6 +709,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -583,3698 +728,6 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -4289,12 +742,12 @@
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1078">
+            <xdr:cNvPr hidden="1" name="A1" id="1025">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
+                  <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4375,12 +828,12 @@
           <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1079">
+            <xdr:cNvPr hidden="1" name="A2" id="1026">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
+                  <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4461,12 +914,12 @@
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1080">
+            <xdr:cNvPr hidden="1" name="A3" id="1027">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
+                  <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4547,12 +1000,12 @@
           <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1081">
+            <xdr:cNvPr hidden="1" name="A4" id="1028">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
+                  <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4633,12 +1086,12 @@
           <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1082">
+            <xdr:cNvPr hidden="1" name="A5" id="1029">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
+                  <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4719,12 +1172,12 @@
           <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1083">
+            <xdr:cNvPr hidden="1" name="A6" id="1030">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
+                  <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4805,12 +1258,12 @@
           <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1084">
+            <xdr:cNvPr hidden="1" name="A7" id="1031">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
+                  <a14:compatExt spid="_x0000_s1031"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4891,12 +1344,12 @@
           <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1085">
+            <xdr:cNvPr hidden="1" name="A8" id="1032">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
+                  <a14:compatExt spid="_x0000_s1032"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4977,12 +1430,12 @@
           <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1086">
+            <xdr:cNvPr hidden="1" name="A9" id="1033">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
+                  <a14:compatExt spid="_x0000_s1033"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5063,12 +1516,12 @@
           <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1087">
+            <xdr:cNvPr hidden="1" name="A10" id="1034">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
+                  <a14:compatExt spid="_x0000_s1034"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5149,12 +1602,12 @@
           <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1088">
+            <xdr:cNvPr hidden="1" name="A11" id="1035">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
+                  <a14:compatExt spid="_x0000_s1035"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5235,12 +1688,12 @@
           <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1089">
+            <xdr:cNvPr hidden="1" name="A12" id="1036">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
+                  <a14:compatExt spid="_x0000_s1036"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5321,12 +1774,12 @@
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1090">
+            <xdr:cNvPr hidden="1" name="A13" id="1037">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1037"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5407,12 +1860,12 @@
           <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1091">
+            <xdr:cNvPr hidden="1" name="A14" id="1038">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
+                  <a14:compatExt spid="_x0000_s1038"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5493,12 +1946,12 @@
           <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1092">
+            <xdr:cNvPr hidden="1" name="A15" id="1039">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1039"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5579,12 +2032,12 @@
           <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1093">
+            <xdr:cNvPr hidden="1" name="A16" id="1040">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1040"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5665,12 +2118,12 @@
           <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1094">
+            <xdr:cNvPr hidden="1" name="A17" id="1041">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1041"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5751,12 +2204,12 @@
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1095">
+            <xdr:cNvPr hidden="1" name="A18" id="1042">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1042"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5837,12 +2290,12 @@
           <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1096">
+            <xdr:cNvPr hidden="1" name="A19" id="1043">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
+                  <a14:compatExt spid="_x0000_s1043"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5923,12 +2376,12 @@
           <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1097">
+            <xdr:cNvPr hidden="1" name="A20" id="1044">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
+                  <a14:compatExt spid="_x0000_s1044"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6009,12 +2462,12 @@
           <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1098">
+            <xdr:cNvPr hidden="1" name="A21" id="1045">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
+                  <a14:compatExt spid="_x0000_s1045"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6095,12 +2548,12 @@
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1099">
+            <xdr:cNvPr hidden="1" name="A22" id="1046">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
+                  <a14:compatExt spid="_x0000_s1046"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6181,12 +2634,12 @@
           <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1100">
+            <xdr:cNvPr hidden="1" name="A23" id="1047">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
+                  <a14:compatExt spid="_x0000_s1047"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6267,12 +2720,12 @@
           <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1101">
+            <xdr:cNvPr hidden="1" name="A24" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
+                  <a14:compatExt spid="_x0000_s1048"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6353,12 +2806,12 @@
           <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1102">
+            <xdr:cNvPr hidden="1" name="A25" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
+                  <a14:compatExt spid="_x0000_s1049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6439,12 +2892,12 @@
           <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1103">
+            <xdr:cNvPr hidden="1" name="A26" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
+                  <a14:compatExt spid="_x0000_s1050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6525,12 +2978,12 @@
           <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1104">
+            <xdr:cNvPr hidden="1" name="A27" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
+                  <a14:compatExt spid="_x0000_s1051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6611,12 +3064,12 @@
           <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1105">
+            <xdr:cNvPr hidden="1" name="A28" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
+                  <a14:compatExt spid="_x0000_s1052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6697,12 +3150,12 @@
           <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1106">
+            <xdr:cNvPr hidden="1" name="A29" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
+                  <a14:compatExt spid="_x0000_s1053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6783,12 +3236,12 @@
           <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1107">
+            <xdr:cNvPr hidden="1" name="A30" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
+                  <a14:compatExt spid="_x0000_s1054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6869,12 +3322,12 @@
           <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1108">
+            <xdr:cNvPr hidden="1" name="A31" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
+                  <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6955,12 +3408,12 @@
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1109">
+            <xdr:cNvPr hidden="1" name="A32" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
+                  <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7041,12 +3494,12 @@
           <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1110">
+            <xdr:cNvPr hidden="1" name="A33" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
+                  <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7127,12 +3580,12 @@
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1111">
+            <xdr:cNvPr hidden="1" name="A34" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
+                  <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7213,12 +3666,12 @@
           <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1112">
+            <xdr:cNvPr hidden="1" name="A35" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
+                  <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7299,12 +3752,12 @@
           <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1113">
+            <xdr:cNvPr hidden="1" name="A36" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7385,12 +3838,12 @@
           <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1114">
+            <xdr:cNvPr hidden="1" name="A37" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7471,12 +3924,12 @@
           <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1115">
+            <xdr:cNvPr hidden="1" name="A38" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7557,12 +4010,12 @@
           <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1116">
+            <xdr:cNvPr hidden="1" name="A39" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7643,12 +4096,12 @@
           <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1117">
+            <xdr:cNvPr hidden="1" name="A40" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7729,12 +4182,12 @@
           <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1118">
+            <xdr:cNvPr hidden="1" name="A41" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7815,12 +4268,12 @@
           <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1119">
+            <xdr:cNvPr hidden="1" name="A42" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7901,12 +4354,12 @@
           <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1120">
+            <xdr:cNvPr hidden="1" name="A43" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7987,12 +4440,12 @@
           <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1121">
+            <xdr:cNvPr hidden="1" name="A44" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8073,12 +4526,12 @@
           <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1122">
+            <xdr:cNvPr hidden="1" name="A45" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8159,12 +4612,12 @@
           <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1123">
+            <xdr:cNvPr hidden="1" name="A46" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8245,12 +4698,12 @@
           <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1124">
+            <xdr:cNvPr hidden="1" name="A47" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8331,12 +4784,12 @@
           <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1125">
+            <xdr:cNvPr hidden="1" name="A48" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8417,12 +4870,12 @@
           <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1126">
+            <xdr:cNvPr hidden="1" name="A49" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8503,12 +4956,12 @@
           <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1127">
+            <xdr:cNvPr hidden="1" name="A50" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8589,12 +5042,12 @@
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1128">
+            <xdr:cNvPr hidden="1" name="A51" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8675,12 +5128,12 @@
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1129">
+            <xdr:cNvPr hidden="1" name="A52" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8761,12 +5214,12 @@
           <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1130">
+            <xdr:cNvPr hidden="1" name="A53" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8847,12 +5300,12 @@
           <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1131">
+            <xdr:cNvPr hidden="1" name="A54" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8933,12 +5386,12 @@
           <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1132">
+            <xdr:cNvPr hidden="1" name="A55" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9019,12 +5472,12 @@
           <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1133">
+            <xdr:cNvPr hidden="1" name="A56" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9105,12 +5558,12 @@
           <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1134">
+            <xdr:cNvPr hidden="1" name="A57" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9191,12 +5644,12 @@
           <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1135">
+            <xdr:cNvPr hidden="1" name="A58" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9277,12 +5730,12 @@
           <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1136">
+            <xdr:cNvPr hidden="1" name="A59" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9363,12 +5816,12 @@
           <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1137">
+            <xdr:cNvPr hidden="1" name="A60" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9449,12 +5902,12 @@
           <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1138">
+            <xdr:cNvPr hidden="1" name="A61" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9535,12 +5988,12 @@
           <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1139">
+            <xdr:cNvPr hidden="1" name="A62" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9621,12 +6074,12 @@
           <xdr:row>63</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1140">
+            <xdr:cNvPr hidden="1" name="A63" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9707,12 +6160,12 @@
           <xdr:row>64</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1141">
+            <xdr:cNvPr hidden="1" name="A64" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9793,12 +6246,12 @@
           <xdr:row>65</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1142">
+            <xdr:cNvPr hidden="1" name="A65" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9879,12 +6332,12 @@
           <xdr:row>66</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1143">
+            <xdr:cNvPr hidden="1" name="A66" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9965,12 +6418,12 @@
           <xdr:row>67</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A67" id="1144">
+            <xdr:cNvPr hidden="1" name="A67" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10051,12 +6504,12 @@
           <xdr:row>68</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A68" id="1145">
+            <xdr:cNvPr hidden="1" name="A68" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10122,629 +6575,656 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.737557547433" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1" style="1"/>
+    <col min="2" max="2" width="45" customWidth="1" style="1"/>
+    <col min="3" max="3" width="60" customWidth="1" style="1"/>
+    <col min="4" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>1</v>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>1</v>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>1</v>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>1</v>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>1</v>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>1</v>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1"/>
-      <c r="B12" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>1</v>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1"/>
-      <c r="B13" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
-      <c r="B14" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>1</v>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>1</v>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>1</v>
+      <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>1</v>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>1</v>
+      <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>1</v>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>1</v>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>1</v>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>1</v>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>1</v>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>1</v>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>1</v>
+      <c r="B29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>1</v>
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>1</v>
+      <c r="B31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1"/>
-      <c r="B32" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>1</v>
+      <c r="B32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
-      <c r="B33" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>1</v>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
-      <c r="B34" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>1</v>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>1</v>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1"/>
-      <c r="B36" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>1</v>
+      <c r="B36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1"/>
-      <c r="B37" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>1</v>
+      <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1"/>
-      <c r="B38" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>1</v>
+      <c r="B38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1"/>
-      <c r="B39" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>1</v>
+      <c r="B39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1"/>
-      <c r="B40" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>1</v>
+      <c r="B40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1"/>
-      <c r="B41" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>1</v>
+      <c r="B41" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1"/>
-      <c r="B42" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>1</v>
+      <c r="B42" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1"/>
-      <c r="B43" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>1</v>
+      <c r="B43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1"/>
-      <c r="B44" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>1</v>
+      <c r="B44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>1</v>
+      <c r="B45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>1</v>
+      <c r="B46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>1</v>
+      <c r="B47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>1</v>
+      <c r="B48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>1</v>
+      <c r="B49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>1</v>
+      <c r="B50" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>1</v>
+      <c r="B51" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>1</v>
+      <c r="B52" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>1</v>
+      <c r="B53" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>1</v>
+      <c r="B54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>1</v>
+      <c r="B55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>1</v>
+      <c r="B56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>1</v>
+      <c r="B57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>1</v>
+      <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>1</v>
+      <c r="B59" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>1</v>
+      <c r="B60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>1</v>
+      <c r="B61" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>1</v>
+      <c r="B62" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>1</v>
+      <c r="B63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>1</v>
+      <c r="B64" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>1</v>
+      <c r="B65" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>1</v>
+      <c r="B66" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1"/>
-      <c r="B67" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>1</v>
+      <c r="B67" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1"/>
-      <c r="B68" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>1</v>
+      <c r="B68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -10756,7 +7236,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId910" name="A1">
+            <control shapeId="1025" r:id="rId2" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10778,7 +7258,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId911" name="A2">
+            <control shapeId="1026" r:id="rId4" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10800,7 +7280,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId912" name="A3">
+            <control shapeId="1027" r:id="rId5" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10822,7 +7302,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId913" name="A4">
+            <control shapeId="1028" r:id="rId6" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10844,7 +7324,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId914" name="A5">
+            <control shapeId="1029" r:id="rId7" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10866,7 +7346,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId915" name="A6">
+            <control shapeId="1030" r:id="rId8" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10888,7 +7368,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId916" name="A7">
+            <control shapeId="1031" r:id="rId9" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10910,7 +7390,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId917" name="A8">
+            <control shapeId="1032" r:id="rId10" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10932,7 +7412,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId918" name="A9">
+            <control shapeId="1033" r:id="rId11" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10954,7 +7434,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId919" name="A10">
+            <control shapeId="1034" r:id="rId12" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10976,7 +7456,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId920" name="A11">
+            <control shapeId="1035" r:id="rId13" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10998,7 +7478,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId921" name="A12">
+            <control shapeId="1036" r:id="rId14" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11020,7 +7500,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId922" name="A13">
+            <control shapeId="1037" r:id="rId15" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11042,7 +7522,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId923" name="A14">
+            <control shapeId="1038" r:id="rId16" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11064,7 +7544,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId924" name="A15">
+            <control shapeId="1039" r:id="rId17" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11086,7 +7566,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId925" name="A16">
+            <control shapeId="1040" r:id="rId18" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11108,7 +7588,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId926" name="A17">
+            <control shapeId="1041" r:id="rId19" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11130,7 +7610,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId927" name="A18">
+            <control shapeId="1042" r:id="rId20" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11152,7 +7632,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId928" name="A19">
+            <control shapeId="1043" r:id="rId21" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11174,7 +7654,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId929" name="A20">
+            <control shapeId="1044" r:id="rId22" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11196,7 +7676,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId930" name="A21">
+            <control shapeId="1045" r:id="rId23" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11218,7 +7698,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId931" name="A22">
+            <control shapeId="1046" r:id="rId24" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11240,7 +7720,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId932" name="A23">
+            <control shapeId="1047" r:id="rId25" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11262,7 +7742,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId933" name="A24">
+            <control shapeId="1048" r:id="rId26" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11284,7 +7764,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId934" name="A25">
+            <control shapeId="1049" r:id="rId27" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11306,7 +7786,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId935" name="A26">
+            <control shapeId="1050" r:id="rId28" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11328,7 +7808,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId936" name="A27">
+            <control shapeId="1051" r:id="rId29" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11350,7 +7830,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId937" name="A28">
+            <control shapeId="1052" r:id="rId30" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11372,7 +7852,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId938" name="A29">
+            <control shapeId="1053" r:id="rId31" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11394,7 +7874,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId939" name="A30">
+            <control shapeId="1054" r:id="rId32" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11416,7 +7896,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId940" name="A31">
+            <control shapeId="1055" r:id="rId33" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11438,7 +7918,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId941" name="A32">
+            <control shapeId="1056" r:id="rId34" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11460,7 +7940,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId942" name="A33">
+            <control shapeId="1057" r:id="rId35" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11482,7 +7962,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId943" name="A34">
+            <control shapeId="1058" r:id="rId36" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11504,7 +7984,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId944" name="A35">
+            <control shapeId="1059" r:id="rId37" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11526,7 +8006,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId945" name="A36">
+            <control shapeId="1060" r:id="rId38" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11548,7 +8028,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId946" name="A37">
+            <control shapeId="1061" r:id="rId39" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11570,7 +8050,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId947" name="A38">
+            <control shapeId="1062" r:id="rId40" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11592,7 +8072,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId948" name="A39">
+            <control shapeId="1063" r:id="rId41" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11614,7 +8094,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId949" name="A40">
+            <control shapeId="1064" r:id="rId42" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11636,7 +8116,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId950" name="A41">
+            <control shapeId="1065" r:id="rId43" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11658,7 +8138,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId951" name="A42">
+            <control shapeId="1066" r:id="rId44" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11680,7 +8160,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId952" name="A43">
+            <control shapeId="1067" r:id="rId45" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11702,7 +8182,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId953" name="A44">
+            <control shapeId="1068" r:id="rId46" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11724,7 +8204,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId954" name="A45">
+            <control shapeId="1069" r:id="rId47" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11746,7 +8226,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId955" name="A46">
+            <control shapeId="1070" r:id="rId48" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11768,7 +8248,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId956" name="A47">
+            <control shapeId="1071" r:id="rId49" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11790,7 +8270,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId957" name="A48">
+            <control shapeId="1072" r:id="rId50" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11812,7 +8292,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId958" name="A49">
+            <control shapeId="1073" r:id="rId51" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11834,7 +8314,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId959" name="A50">
+            <control shapeId="1074" r:id="rId52" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11856,7 +8336,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId960" name="A51">
+            <control shapeId="1075" r:id="rId53" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11878,7 +8358,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId961" name="A52">
+            <control shapeId="1076" r:id="rId54" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11900,7 +8380,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId962" name="A53">
+            <control shapeId="1077" r:id="rId55" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11922,7 +8402,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId963" name="A54">
+            <control shapeId="1078" r:id="rId56" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11944,7 +8424,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId964" name="A55">
+            <control shapeId="1079" r:id="rId57" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11966,7 +8446,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId965" name="A56">
+            <control shapeId="1080" r:id="rId58" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11988,7 +8468,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId966" name="A57">
+            <control shapeId="1081" r:id="rId59" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12010,7 +8490,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId967" name="A58">
+            <control shapeId="1082" r:id="rId60" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12032,7 +8512,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId968" name="A59">
+            <control shapeId="1083" r:id="rId61" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12054,7 +8534,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId969" name="A60">
+            <control shapeId="1084" r:id="rId62" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12076,7 +8556,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId970" name="A61">
+            <control shapeId="1085" r:id="rId63" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12098,7 +8578,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId971" name="A62">
+            <control shapeId="1086" r:id="rId64" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12120,7 +8600,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId972" name="A63">
+            <control shapeId="1087" r:id="rId65" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12142,7 +8622,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId973" name="A64">
+            <control shapeId="1088" r:id="rId66" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12164,7 +8644,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId974" name="A65">
+            <control shapeId="1089" r:id="rId67" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12186,7 +8666,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId975" name="A66">
+            <control shapeId="1090" r:id="rId68" name="A66">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12208,7 +8688,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId976" name="A67">
+            <control shapeId="1091" r:id="rId69" name="A67">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12230,7 +8710,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId977" name="A68">
+            <control shapeId="1092" r:id="rId70" name="A68">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12243,6 +8723,28 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
